--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WYOMING_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WYOMING_2014.xlsx
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C44">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C70">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C105">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C297">
